--- a/ejemplos/2_Recursos_Humanos/04_Evaluacion_de_Desempeno_EJEMPLO.xlsx
+++ b/ejemplos/2_Recursos_Humanos/04_Evaluacion_de_Desempeno_EJEMPLO.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTADA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMATO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,90 +31,155 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="001B6B73"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="30"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <i val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="26"/>
+      <color rgb="001B6B73"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00C9D3DB"/>
+      <name val="Abadi"/>
+      <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001B6B73"/>
+      <name val="Abadi"/>
+      <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C9A227"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="002B2B2B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="005B6B78"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="008A97A3"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -148,7 +215,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -210,14 +277,102 @@
       <bottom style="thin"/>
     </border>
     <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
       <top style="thick">
         <color rgb="00C9A227"/>
       </top>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="00C9A227"/>
-      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
     </border>
     <border>
       <left/>
@@ -354,32 +509,155 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -389,23 +667,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="27" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="27" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -413,43 +691,100 @@
     <xf numFmtId="2" fontId="7" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="27" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="6" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,6 +860,122 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Calificación por criterio (1 a 5)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'RESUMEN'!C25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1B6B73"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1B6B73"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'RESUMEN'!$B$26:$B$33</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'RESUMEN'!$C$26:$C$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="5"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8460000" cy="3096000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -817,22 +1268,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -841,154 +1298,462 @@
       </c>
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>VERSIÓN 2.0  ·  MÉXICO</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
       <c r="D3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Evaluación de desempeño</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>EVALUACIÓN DE DESEMPEÑO</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Formato administrativo editable · México</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-    </row>
-    <row r="6">
+      <c r="G5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Formato administrativo profesional · editable · listo para imprimir</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="n"/>
       <c r="D7" s="1" t="n"/>
-    </row>
-    <row r="8" ht="6" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>FÓRMULAS AUTOMÁTICAS</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>LISTAS DESPLEGABLES</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>HOJAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>LISTO PARA IMPRIMIR</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="6" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>¿QUÉ INCLUYE ESTE ARCHIVO?</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>FORMATO</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Hoja principal de captura. Aquí registras tu información; las celdas grises calculan solas.</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>RESUMEN</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Tablero con indicadores y gráficas que se actualizan automáticamente con tus datos.</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>AYUDA</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Preguntas frecuentes, glosario y lista de verificación para cerrar tu periodo.</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>CÓMO USARLO</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="7" t="n">
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Llena los datos del empleado y califica cada criterio de 1 a 5.</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="B12" s="7" t="n">
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Los pesos suman 100% y pueden modificarse; cuida que el total siga siendo 100%.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="7" t="n">
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>El resultado ponderado y la categoría se calculan automáticamente.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="7" t="n">
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Documenta fortalezas y plan de acción antes de recabar firmas.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="B15" s="7" t="n">
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>LEYENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Celda de captura: escribe aquí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="11" t="inlineStr"/>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Cálculo automático: no la modifiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Encabezados y títulos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
-        </is>
-      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Evalúa con hechos y ejemplos, no con impresiones; anota evidencia en la columna de comentarios.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Comparte los criterios con el empleado al inicio del periodo.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Realiza la entrevista de retroalimentación dentro de la semana siguiente a la evaluación.</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Los pesos de los criterios deben sumar 100%.</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="17" t="inlineStr"/>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="19" t="inlineStr"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="16">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="C28:F28"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -1013,12 +1778,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>EVALUACIÓN DE DESEMPEÑO</t>
         </is>
       </c>
-      <c r="F1" s="34" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
@@ -1026,401 +1791,487 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>Califica de 1 (deficiente) a 5 (sobresaliente)</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="36" t="n"/>
+      <c r="B2" s="64" t="n"/>
+      <c r="C2" s="64" t="n"/>
+      <c r="D2" s="64" t="n"/>
+      <c r="E2" s="64" t="n"/>
+      <c r="F2" s="65" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>Empleado</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Ana López Ramírez</t>
-        </is>
-      </c>
-      <c r="C4" s="37" t="n"/>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>Puesto</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Coordinadora administrativa</t>
-        </is>
-      </c>
-      <c r="F4" s="37" t="n"/>
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>EMPLEADO</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>ANA LÓPEZ RAMÍREZ</t>
+        </is>
+      </c>
+      <c r="C4" s="66" t="n"/>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>PUESTO</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>COORDINADORA ADMINISTRATIVA</t>
+        </is>
+      </c>
+      <c r="F4" s="66" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Área</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Administración</t>
-        </is>
-      </c>
-      <c r="C5" s="37" t="n"/>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>Periodo</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Enero - Junio 2026</t>
-        </is>
-      </c>
-      <c r="F5" s="37" t="n"/>
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>ÁREA</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C5" s="66" t="n"/>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>PERIODO</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>ENERO - JUNIO 2026</t>
+        </is>
+      </c>
+      <c r="F5" s="66" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Evaluador</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Lic. Jorge Medina</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="n"/>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="n">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>EVALUADOR</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>LIC. JORGE MEDINA</t>
+        </is>
+      </c>
+      <c r="C6" s="66" t="n"/>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="n">
         <v>46206</v>
       </c>
-      <c r="F6" s="37" t="n"/>
+      <c r="F6" s="66" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>Criterio</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>Calificación (1-5)</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>Peso %</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>Ponderado</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>Comentarios</t>
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>CRITERIO</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>CALIFICACIÓN (1-5)</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>PESO %</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>PONDERADO</t>
+        </is>
+      </c>
+      <c r="F8" s="29" t="inlineStr">
+        <is>
+          <t>COMENTARIOS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="n">
+      <c r="A9" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Calidad del trabajo</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL TRABAJO</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="33">
         <f>IF(C9="","",C9*D9)</f>
         <v/>
       </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Cero errores en cierres mensuales.</t>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>CERO ERRORES EN CIERRES MENSUALES.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Cumplimiento de objetivos</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n">
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>CUMPLIMIENTO DE OBJETIVOS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="33">
         <f>IF(C10="","",C10*D10)</f>
         <v/>
       </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Cumplió 96% de objetivos.</t>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>CUMPLIÓ 96% DE OBJETIVOS.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Productividad y orden</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>PRODUCTIVIDAD Y ORDEN</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="33">
         <f>IF(C11="","",C11*D11)</f>
         <v/>
       </c>
-      <c r="F11" s="9" t="n"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="n">
+      <c r="A12" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Trabajo en equipo</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n">
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>TRABAJO EN EQUIPO</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="33">
         <f>IF(C12="","",C12*D12)</f>
         <v/>
       </c>
-      <c r="F12" s="9" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n">
+      <c r="A13" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Comunicación</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="33">
         <f>IF(C13="","",C13*D13)</f>
         <v/>
       </c>
-      <c r="F13" s="9" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>Iniciativa y proactividad</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n">
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>INICIATIVA Y PROACTIVIDAD</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="33">
         <f>IF(C14="","",C14*D14)</f>
         <v/>
       </c>
-      <c r="F14" s="9" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>Puntualidad y asistencia</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>PUNTUALIDAD Y ASISTENCIA</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="33">
         <f>IF(C15="","",C15*D15)</f>
         <v/>
       </c>
-      <c r="F15" s="9" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>Apego a políticas y valores</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n">
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>APEGO A POLÍTICAS Y VALORES</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="33">
         <f>IF(C16="","",C16*D16)</f>
         <v/>
       </c>
-      <c r="F16" s="9" t="n"/>
+      <c r="F16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="C17" s="27" t="inlineStr">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>RESULTADO</t>
         </is>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="35">
         <f>SUM(D9:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="36">
         <f>SUM(E9:E16)</f>
         <v/>
       </c>
+      <c r="F17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="30">
-        <f>IF(COUNT(C9:C16)=0,"",IF(E17&gt;=4.5,"Sobresaliente",IF(E17&gt;=3.5,"Satisfactorio",IF(E17&gt;=2.5,"Requiere mejora","Deficiente"))))</f>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="37">
+        <f>IF(COUNT(C9:C16)=0,"",IF(E17&gt;=4.5,"SOBRESALIENTE",IF(E17&gt;=3.5,"SATISFACTORIO",IF(E17&gt;=2.5,"REQUIERE MEJORA","DEFICIENTE"))))</f>
         <v/>
       </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>Fortalezas</t>
-        </is>
-      </c>
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>FORTALEZAS</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Excelente organización, cumple fechas límite y apoya a su equipo.</t>
-        </is>
-      </c>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="38" t="n"/>
-      <c r="F21" s="39" t="n"/>
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>EXCELENTE ORGANIZACIÓN, CUMPLE FECHAS LÍMITE Y APOYA A SU EQUIPO.</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="n"/>
+      <c r="D21" s="67" t="n"/>
+      <c r="E21" s="67" t="n"/>
+      <c r="F21" s="68" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="40" t="n"/>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="41" t="n"/>
-      <c r="E22" s="41" t="n"/>
-      <c r="F22" s="42" t="n"/>
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="69" t="n"/>
+      <c r="C22" s="70" t="n"/>
+      <c r="D22" s="70" t="n"/>
+      <c r="E22" s="70" t="n"/>
+      <c r="F22" s="71" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="43" t="n"/>
-      <c r="C23" s="44" t="n"/>
-      <c r="D23" s="44" t="n"/>
-      <c r="E23" s="44" t="n"/>
-      <c r="F23" s="45" t="n"/>
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="72" t="n"/>
+      <c r="C23" s="73" t="n"/>
+      <c r="D23" s="73" t="n"/>
+      <c r="E23" s="73" t="n"/>
+      <c r="F23" s="74" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>Áreas de oportunidad / plan de acción</t>
-        </is>
-      </c>
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="38" t="inlineStr">
+        <is>
+          <t>ÁREAS DE OPORTUNIDAD / PLAN DE ACCIÓN</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Fortalecer delegación de tareas; curso de liderazgo en el segundo semestre.</t>
-        </is>
-      </c>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="38" t="n"/>
-      <c r="E26" s="38" t="n"/>
-      <c r="F26" s="39" t="n"/>
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>FORTALECER DELEGACIÓN DE TAREAS; CURSO DE LIDERAZGO EN EL SEGUNDO SEMESTRE.</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="n"/>
+      <c r="D26" s="67" t="n"/>
+      <c r="E26" s="67" t="n"/>
+      <c r="F26" s="68" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="40" t="n"/>
-      <c r="C27" s="41" t="n"/>
-      <c r="D27" s="41" t="n"/>
-      <c r="E27" s="41" t="n"/>
-      <c r="F27" s="42" t="n"/>
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="69" t="n"/>
+      <c r="C27" s="70" t="n"/>
+      <c r="D27" s="70" t="n"/>
+      <c r="E27" s="70" t="n"/>
+      <c r="F27" s="71" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="43" t="n"/>
-      <c r="C28" s="44" t="n"/>
-      <c r="D28" s="44" t="n"/>
-      <c r="E28" s="44" t="n"/>
-      <c r="F28" s="45" t="n"/>
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="72" t="n"/>
+      <c r="C28" s="73" t="n"/>
+      <c r="D28" s="73" t="n"/>
+      <c r="E28" s="73" t="n"/>
+      <c r="F28" s="74" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="E32" s="32" t="n"/>
+      <c r="A32" s="39" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="39" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="inlineStr">
-        <is>
-          <t>Evaluado</t>
-        </is>
-      </c>
-      <c r="C33" s="33" t="inlineStr">
-        <is>
-          <t>Evaluador</t>
-        </is>
-      </c>
-      <c r="E33" s="33" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t>EVALUADO</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>EVALUADOR</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="40" t="inlineStr">
         <is>
           <t>RH</t>
         </is>
       </c>
+      <c r="F33" s="4" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -1460,4 +2311,910 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>RESUMEN DE LA EVALUACIÓN</t>
+        </is>
+      </c>
+      <c r="H1" s="62" t="inlineStr">
+        <is>
+          <t>INSERTE SU LOGO
+(clic derecho &gt; Insertar imagen)</t>
+        </is>
+      </c>
+      <c r="I1" s="75" t="n"/>
+      <c r="J1" s="76" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="63" t="inlineStr">
+        <is>
+          <t>Resultado por criterio y calificación global</t>
+        </is>
+      </c>
+      <c r="B2" s="64" t="n"/>
+      <c r="C2" s="64" t="n"/>
+      <c r="D2" s="64" t="n"/>
+      <c r="E2" s="64" t="n"/>
+      <c r="F2" s="64" t="n"/>
+      <c r="G2" s="64" t="n"/>
+      <c r="H2" s="77" t="n"/>
+      <c r="I2" s="78" t="n"/>
+      <c r="J2" s="79" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="80" t="inlineStr">
+        <is>
+          <t>RESULTADO GLOBAL</t>
+        </is>
+      </c>
+      <c r="C4" s="81" t="n"/>
+      <c r="D4" s="80" t="inlineStr">
+        <is>
+          <t>CATEGORÍA</t>
+        </is>
+      </c>
+      <c r="E4" s="81" t="n"/>
+      <c r="F4" s="80" t="inlineStr">
+        <is>
+          <t>MEJOR CRITERIO</t>
+        </is>
+      </c>
+      <c r="G4" s="81" t="n"/>
+      <c r="H4" s="80" t="inlineStr">
+        <is>
+          <t>A MEJORAR</t>
+        </is>
+      </c>
+      <c r="I4" s="81" t="n"/>
+      <c r="J4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="82">
+        <f>IF(COUNT(FORMATO!C9:C16)=0,0,FORMATO!E17)</f>
+        <v/>
+      </c>
+      <c r="C5" s="83" t="n"/>
+      <c r="D5" s="84">
+        <f>FORMATO!B18</f>
+        <v/>
+      </c>
+      <c r="E5" s="83" t="n"/>
+      <c r="F5" s="84">
+        <f>IFERROR(INDEX(B26:B33,MATCH(MAX(C26:C33),C26:C33,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="83" t="n"/>
+      <c r="H5" s="84">
+        <f>IF(COUNT(C26:C33)=0,"",IFERROR(INDEX(B26:B33,MATCH(MIN(C26:C33),C26:C33,0)),""))</f>
+        <v/>
+      </c>
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>CRITERIO</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>CALIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="52">
+        <f>FORMATO!B9</f>
+        <v/>
+      </c>
+      <c r="C26" s="53">
+        <f>IF(FORMATO!C9="",0,FORMATO!C9)</f>
+        <v/>
+      </c>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="52">
+        <f>FORMATO!B10</f>
+        <v/>
+      </c>
+      <c r="C27" s="53">
+        <f>IF(FORMATO!C10="",0,FORMATO!C10)</f>
+        <v/>
+      </c>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="52">
+        <f>FORMATO!B11</f>
+        <v/>
+      </c>
+      <c r="C28" s="53">
+        <f>IF(FORMATO!C11="",0,FORMATO!C11)</f>
+        <v/>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="52">
+        <f>FORMATO!B12</f>
+        <v/>
+      </c>
+      <c r="C29" s="53">
+        <f>IF(FORMATO!C12="",0,FORMATO!C12)</f>
+        <v/>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="52">
+        <f>FORMATO!B13</f>
+        <v/>
+      </c>
+      <c r="C30" s="53">
+        <f>IF(FORMATO!C13="",0,FORMATO!C13)</f>
+        <v/>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="52">
+        <f>FORMATO!B14</f>
+        <v/>
+      </c>
+      <c r="C31" s="53">
+        <f>IF(FORMATO!C14="",0,FORMATO!C14)</f>
+        <v/>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="52">
+        <f>FORMATO!B15</f>
+        <v/>
+      </c>
+      <c r="C32" s="53">
+        <f>IF(FORMATO!C15="",0,FORMATO!C15)</f>
+        <v/>
+      </c>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="52">
+        <f>FORMATO!B16</f>
+        <v/>
+      </c>
+      <c r="C33" s="53">
+        <f>IF(FORMATO!C16="",0,FORMATO!C16)</f>
+        <v/>
+      </c>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="11">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H1:J2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Página &amp;P&amp;R&amp;8 Impreso: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B6B73"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="54" t="inlineStr">
+        <is>
+          <t>AYUDA Y PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="55" t="inlineStr">
+        <is>
+          <t>EVALUACIÓN DE DESEMPEÑO</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>¿Puedo cambiar los criterios?</t>
+        </is>
+      </c>
+      <c r="D6" s="57" t="inlineStr">
+        <is>
+          <t>Sí, edita el nombre y el peso; verifica que el total sea 100%.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>¿Qué hago con una calificación baja?</t>
+        </is>
+      </c>
+      <c r="D7" s="57" t="inlineStr">
+        <is>
+          <t>Acuerda un plan de acción con metas medibles y fecha de revisión.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t>¿Por qué no puedo escribir en algunas celdas?</t>
+        </is>
+      </c>
+      <c r="D8" s="57" t="inlineStr">
+        <is>
+          <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>¿Cómo agrego mi logotipo?</t>
+        </is>
+      </c>
+      <c r="D9" s="57" t="inlineStr">
+        <is>
+          <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
+        </is>
+      </c>
+      <c r="D10" s="57" t="inlineStr">
+        <is>
+          <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>¿Con qué versiones de Excel funciona?</t>
+        </is>
+      </c>
+      <c r="D11" s="57" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>¿Por qué la letra se ve diferente?</t>
+        </is>
+      </c>
+      <c r="D12" s="57" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t>¿Puedo usarlo en varias empresas o por varios años?</t>
+        </is>
+      </c>
+      <c r="D13" s="57" t="inlineStr">
+        <is>
+          <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>GLOSARIO</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="58" t="inlineStr">
+        <is>
+          <t>PONDERADO</t>
+        </is>
+      </c>
+      <c r="D16" s="59" t="inlineStr">
+        <is>
+          <t>Calificación x peso del criterio.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="58" t="inlineStr">
+        <is>
+          <t>SOBRESALIENTE</t>
+        </is>
+      </c>
+      <c r="D17" s="59" t="inlineStr">
+        <is>
+          <t>Resultado &gt;= 4.5</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="58" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="D18" s="59" t="inlineStr">
+        <is>
+          <t>Resultado &gt;= 3.5</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="58" t="inlineStr">
+        <is>
+          <t>REQUIERE MEJORA</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Resultado &gt;= 2.5</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="58" t="inlineStr">
+        <is>
+          <t>DEFICIENTE</t>
+        </is>
+      </c>
+      <c r="D20" s="59" t="inlineStr">
+        <is>
+          <t>Resultado &lt; 2.5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>LISTA DE VERIFICACIÓN (marca ☑ al completar)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>Criterios acordados con el empleado</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="60" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C24" s="61" t="inlineStr">
+        <is>
+          <t>Evaluación llenada con evidencias</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C25" s="61" t="inlineStr">
+        <is>
+          <t>Retroalimentación realizada</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="60" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C26" s="61" t="inlineStr">
+        <is>
+          <t>Plan de acción firmado</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B23 B24 B25 B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"☐,☑"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/ejemplos/2_Recursos_Humanos/04_Evaluacion_de_Desempeno_EJEMPLO.xlsx
+++ b/ejemplos/2_Recursos_Humanos/04_Evaluacion_de_Desempeno_EJEMPLO.xlsx
@@ -51,7 +51,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -75,7 +75,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -117,7 +117,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -140,7 +140,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -168,7 +168,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -894,11 +894,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1B6B73"/>
+              <a:srgbClr val="0E7C8B"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="1B6B73"/>
+                <a:srgbClr val="0E7C8B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2855,7 +2855,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/ejemplos/2_Recursos_Humanos/04_Evaluacion_de_Desempeno_EJEMPLO.xlsx
+++ b/ejemplos/2_Recursos_Humanos/04_Evaluacion_de_Desempeno_EJEMPLO.xlsx
@@ -1293,7 +1293,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1728,7 +1728,7 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="G38" s="1" t="n"/>

--- a/ejemplos/2_Recursos_Humanos/04_Evaluacion_de_Desempeno_EJEMPLO.xlsx
+++ b/ejemplos/2_Recursos_Humanos/04_Evaluacion_de_Desempeno_EJEMPLO.xlsx
@@ -12,7 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FORMATO'!$8:$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,158 +33,165 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
-      <sz val="18"/>
+      <sz val="24"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="30"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E7C8B"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
-      <color rgb="002B2B2B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -205,6 +214,16 @@
       </patternFill>
     </fill>
     <fill>
+      <gradientFill type="linear" degree="90">
+        <stop position="0">
+          <color rgb="0017426B"/>
+        </stop>
+        <stop position="1">
+          <color rgb="000B2A4A"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
@@ -215,7 +234,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -274,6 +293,20 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
       <bottom style="thin"/>
     </border>
     <border>
@@ -371,8 +404,22 @@
     </border>
     <border>
       <bottom style="thin">
+        <color rgb="00E3E8ED"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
         <color rgb="00C9D3DB"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E3E8ED"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -615,24 +662,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -643,19 +690,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -667,23 +722,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="28" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="27" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="2" fontId="27" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="28" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="28" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -691,99 +755,100 @@
     <xf numFmtId="2" fontId="7" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="10" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="10" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="27" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="28" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="10" fillId="6" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="7" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="10" fillId="7" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -894,11 +959,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="0E7C8B"/>
+              <a:srgbClr val="12A0A8"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="0E7C8B"/>
+                <a:srgbClr val="12A0A8"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -914,7 +979,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="70"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -939,6 +1004,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8ED"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -948,6 +1023,12 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1268,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1507,7 +1588,7 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>CÓMO USARLO</t>
+          <t>FICHA TÉCNICA</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -1518,62 +1599,87 @@
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Llena los datos del empleado y califica cada criterio de 1 a 5.</t>
-        </is>
-      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Capacidad</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>8 criterios ponderados</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="n"/>
+      <c r="F21" s="67" t="n"/>
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Los pesos suman 100% y pueden modificarse; cuida que el total siga siendo 100%.</t>
-        </is>
-      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Compatibilidad</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac)</t>
+        </is>
+      </c>
+      <c r="E22" s="67" t="n"/>
+      <c r="F22" s="67" t="n"/>
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>El resultado ponderado y la categoría se calculan automáticamente.</t>
-        </is>
-      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Idioma y moneda</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Español (México) · Pesos mexicanos (MXN) · IVA 16%</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="n"/>
+      <c r="F23" s="67" t="n"/>
       <c r="G23" s="4" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Documenta fortalezas y plan de acción antes de recabar firmas.</t>
-        </is>
-      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Protección</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Hojas protegidas sin contraseña (Revisar &gt; Desproteger hoja)</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="n"/>
+      <c r="F24" s="67" t="n"/>
       <c r="G24" s="4" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="21" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Arial (disponible en Windows, Mac y Google Sheets)</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="n"/>
+      <c r="F25" s="67" t="n"/>
       <c r="G25" s="4" t="n"/>
     </row>
     <row r="26">
@@ -1589,7 +1695,7 @@
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>RECOMENDACIONES DE USO</t>
+          <t>CÓMO USARLO</t>
         </is>
       </c>
       <c r="C27" s="10" t="n"/>
@@ -1600,159 +1706,264 @@
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B28" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Evalúa con hechos y ejemplos, no con impresiones; anota evidencia en la columna de comentarios.</t>
+          <t>Llena los datos del empleado y califica cada criterio de 1 a 5.</t>
         </is>
       </c>
       <c r="G28" s="4" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B29" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Comparte los criterios con el empleado al inicio del periodo.</t>
+          <t>Los pesos suman 100% y pueden modificarse; cuida que el total siga siendo 100%.</t>
         </is>
       </c>
       <c r="G29" s="4" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B30" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Realiza la entrevista de retroalimentación dentro de la semana siguiente a la evaluación.</t>
+          <t>El resultado ponderado y la categoría se calculan automáticamente.</t>
         </is>
       </c>
       <c r="G30" s="4" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="4" t="n"/>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Documenta fortalezas y plan de acción antes de recabar firmas.</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Evalúa con hechos y ejemplos, no con impresiones; anota evidencia en la columna de comentarios.</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Comparte los criterios con el empleado al inicio del periodo.</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Realiza la entrevista de retroalimentación dentro de la semana siguiente a la evaluación.</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Los pesos de los criterios deben sumar 100%.</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="17" t="inlineStr"/>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>CELDA DE CAPTURA: escribe aquí.</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="19" t="inlineStr"/>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="22" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="23" t="inlineStr"/>
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>ENCABEZADOS Y TÍTULOS.</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="24" t="inlineStr"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>* CAMPO OBLIGATORIO: complétalo antes de imprimir o enviar.</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="25" t="inlineStr">
         <is>
           <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
-      <c r="G38" s="1" t="n"/>
+      <c r="G46" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="16">
-    <mergeCell ref="C22:F22"/>
+  <mergeCells count="21">
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B4:F5"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId3"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
@@ -1769,21 +1980,21 @@
   <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.35" customWidth="1" min="1" max="1"/>
+    <col width="13.5" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12.35" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>EVALUACIÓN DE DESEMPEÑO</t>
         </is>
       </c>
-      <c r="F1" s="62" t="inlineStr">
+      <c r="F1" s="68" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
@@ -1791,16 +2002,16 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>Califica de 1 (deficiente) a 5 (sobresaliente)</t>
         </is>
       </c>
-      <c r="B2" s="64" t="n"/>
-      <c r="C2" s="64" t="n"/>
-      <c r="D2" s="64" t="n"/>
-      <c r="E2" s="64" t="n"/>
-      <c r="F2" s="65" t="n"/>
+      <c r="B2" s="70" t="n"/>
+      <c r="C2" s="70" t="n"/>
+      <c r="D2" s="70" t="n"/>
+      <c r="E2" s="70" t="n"/>
+      <c r="F2" s="71" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1811,74 +2022,74 @@
       <c r="F3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>EMPLEADO</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>EMPLEADO *</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>ANA LÓPEZ RAMÍREZ</t>
         </is>
       </c>
-      <c r="C4" s="66" t="n"/>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="C4" s="72" t="n"/>
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>PUESTO</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>COORDINADORA ADMINISTRATIVA</t>
         </is>
       </c>
-      <c r="F4" s="66" t="n"/>
+      <c r="F4" s="72" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>ÁREA</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C5" s="66" t="n"/>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>PERIODO</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="C5" s="72" t="n"/>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>PERIODO *</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>ENERO - JUNIO 2026</t>
         </is>
       </c>
-      <c r="F5" s="66" t="n"/>
+      <c r="F5" s="72" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>EVALUADOR</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>LIC. JORGE MEDINA</t>
         </is>
       </c>
-      <c r="C6" s="66" t="n"/>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="E6" s="28" t="n">
+      <c r="C6" s="72" t="n"/>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>FECHA *</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="n">
         <v>46206</v>
       </c>
-      <c r="F6" s="66" t="n"/>
+      <c r="F6" s="72" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -1888,227 +2099,227 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>CRITERIO</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>CALIFICACIÓN (1-5)</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>PESO %</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>PONDERADO</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>COMENTARIOS</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="30" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>CALIDAD DEL TRABAJO</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="37" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="38">
         <f>IF(C9="","",C9*D9)</f>
         <v/>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>CERO ERRORES EN CIERRES MENSUALES.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="30" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>CUMPLIMIENTO DE OBJETIVOS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="37" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="38">
         <f>IF(C10="","",C10*D10)</f>
         <v/>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>CUMPLIÓ 96% DE OBJETIVOS.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="30" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>PRODUCTIVIDAD Y ORDEN</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" s="37" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="38">
         <f>IF(C11="","",C11*D11)</f>
         <v/>
       </c>
-      <c r="F11" s="17" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="F11" s="36" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>TRABAJO EN EQUIPO</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="37" t="n">
         <v>0.1</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="38">
         <f>IF(C12="","",C12*D12)</f>
         <v/>
       </c>
-      <c r="F12" s="17" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="F12" s="36" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>COMUNICACIÓN</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="37" t="n">
         <v>0.1</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="38">
         <f>IF(C13="","",C13*D13)</f>
         <v/>
       </c>
-      <c r="F13" s="17" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="F13" s="36" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>INICIATIVA Y PROACTIVIDAD</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="37" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="38">
         <f>IF(C14="","",C14*D14)</f>
         <v/>
       </c>
-      <c r="F14" s="17" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="F14" s="36" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>PUNTUALIDAD Y ASISTENCIA</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="37" t="n">
         <v>0.1</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="38">
         <f>IF(C15="","",C15*D15)</f>
         <v/>
       </c>
-      <c r="F15" s="17" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="F15" s="36" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="31" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>APEGO A POLÍTICAS Y VALORES</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="37" t="n">
         <v>0.1</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="38">
         <f>IF(C16="","",C16*D16)</f>
         <v/>
       </c>
-      <c r="F16" s="17" t="n"/>
+      <c r="F16" s="36" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="39" t="inlineStr">
         <is>
           <t>RESULTADO</t>
         </is>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="40">
         <f>SUM(D9:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="41">
         <f>SUM(E9:E16)</f>
         <v/>
       </c>
@@ -2116,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
-      <c r="B18" s="37">
+      <c r="B18" s="42">
         <f>IF(COUNT(C9:C16)=0,"",IF(E17&gt;=4.5,"SOBRESALIENTE",IF(E17&gt;=3.5,"SATISFACTORIO",IF(E17&gt;=2.5,"REQUIERE MEJORA","DEFICIENTE"))))</f>
         <v/>
       </c>
@@ -2135,7 +2346,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
-      <c r="B20" s="38" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>FORTALEZAS</t>
         </is>
@@ -2147,31 +2358,31 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>EXCELENTE ORGANIZACIÓN, CUMPLE FECHAS LÍMITE Y APOYA A SU EQUIPO.</t>
         </is>
       </c>
-      <c r="C21" s="67" t="n"/>
-      <c r="D21" s="67" t="n"/>
-      <c r="E21" s="67" t="n"/>
-      <c r="F21" s="68" t="n"/>
+      <c r="C21" s="73" t="n"/>
+      <c r="D21" s="73" t="n"/>
+      <c r="E21" s="73" t="n"/>
+      <c r="F21" s="74" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="69" t="n"/>
-      <c r="C22" s="70" t="n"/>
-      <c r="D22" s="70" t="n"/>
-      <c r="E22" s="70" t="n"/>
-      <c r="F22" s="71" t="n"/>
+      <c r="B22" s="75" t="n"/>
+      <c r="C22" s="76" t="n"/>
+      <c r="D22" s="76" t="n"/>
+      <c r="E22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="72" t="n"/>
-      <c r="C23" s="73" t="n"/>
-      <c r="D23" s="73" t="n"/>
-      <c r="E23" s="73" t="n"/>
-      <c r="F23" s="74" t="n"/>
+      <c r="B23" s="78" t="n"/>
+      <c r="C23" s="79" t="n"/>
+      <c r="D23" s="79" t="n"/>
+      <c r="E23" s="79" t="n"/>
+      <c r="F23" s="80" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -2183,7 +2394,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>ÁREAS DE OPORTUNIDAD / PLAN DE ACCIÓN</t>
         </is>
@@ -2195,31 +2406,31 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>FORTALECER DELEGACIÓN DE TAREAS; CURSO DE LIDERAZGO EN EL SEGUNDO SEMESTRE.</t>
         </is>
       </c>
-      <c r="C26" s="67" t="n"/>
-      <c r="D26" s="67" t="n"/>
-      <c r="E26" s="67" t="n"/>
-      <c r="F26" s="68" t="n"/>
+      <c r="C26" s="73" t="n"/>
+      <c r="D26" s="73" t="n"/>
+      <c r="E26" s="73" t="n"/>
+      <c r="F26" s="74" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
-      <c r="B27" s="69" t="n"/>
-      <c r="C27" s="70" t="n"/>
-      <c r="D27" s="70" t="n"/>
-      <c r="E27" s="70" t="n"/>
-      <c r="F27" s="71" t="n"/>
+      <c r="B27" s="75" t="n"/>
+      <c r="C27" s="76" t="n"/>
+      <c r="D27" s="76" t="n"/>
+      <c r="E27" s="76" t="n"/>
+      <c r="F27" s="77" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="72" t="n"/>
-      <c r="C28" s="73" t="n"/>
-      <c r="D28" s="73" t="n"/>
-      <c r="E28" s="73" t="n"/>
-      <c r="F28" s="74" t="n"/>
+      <c r="B28" s="78" t="n"/>
+      <c r="C28" s="79" t="n"/>
+      <c r="D28" s="79" t="n"/>
+      <c r="E28" s="79" t="n"/>
+      <c r="F28" s="80" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -2246,27 +2457,27 @@
       <c r="F31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="39" t="n"/>
+      <c r="A32" s="44" t="n"/>
       <c r="B32" s="4" t="n"/>
-      <c r="C32" s="39" t="n"/>
+      <c r="C32" s="44" t="n"/>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="39" t="n"/>
+      <c r="E32" s="44" t="n"/>
       <c r="F32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="inlineStr">
+      <c r="A33" s="45" t="inlineStr">
         <is>
           <t>EVALUADO</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
-      <c r="C33" s="40" t="inlineStr">
+      <c r="C33" s="45" t="inlineStr">
         <is>
           <t>EVALUADOR</t>
         </is>
       </c>
       <c r="D33" s="4" t="n"/>
-      <c r="E33" s="40" t="inlineStr">
+      <c r="E33" s="45" t="inlineStr">
         <is>
           <t>RH</t>
         </is>
@@ -2295,7 +2506,7 @@
     <mergeCell ref="A32"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C9:C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C9:C16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="OPCIÓN NO VÁLIDA" error="Elige una opción de la lista (puedes editarla en la hoja CATÁLOGOS)." promptTitle="SELECCIONA" prompt="Elige una opción de la lista desplegable." type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2336,35 +2547,35 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>RESUMEN DE LA EVALUACIÓN</t>
         </is>
       </c>
-      <c r="H1" s="62" t="inlineStr">
+      <c r="H1" s="68" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="I1" s="75" t="n"/>
-      <c r="J1" s="76" t="n"/>
+      <c r="I1" s="81" t="n"/>
+      <c r="J1" s="82" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>Resultado por criterio y calificación global</t>
         </is>
       </c>
-      <c r="B2" s="64" t="n"/>
-      <c r="C2" s="64" t="n"/>
-      <c r="D2" s="64" t="n"/>
-      <c r="E2" s="64" t="n"/>
-      <c r="F2" s="64" t="n"/>
-      <c r="G2" s="64" t="n"/>
-      <c r="H2" s="77" t="n"/>
-      <c r="I2" s="78" t="n"/>
-      <c r="J2" s="79" t="n"/>
+      <c r="B2" s="70" t="n"/>
+      <c r="C2" s="70" t="n"/>
+      <c r="D2" s="70" t="n"/>
+      <c r="E2" s="70" t="n"/>
+      <c r="F2" s="70" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="83" t="n"/>
+      <c r="I2" s="84" t="n"/>
+      <c r="J2" s="85" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -2378,56 +2589,56 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="n"/>
-      <c r="B4" s="80" t="inlineStr">
+      <c r="B4" s="86" t="inlineStr">
         <is>
           <t>RESULTADO GLOBAL</t>
         </is>
       </c>
-      <c r="C4" s="81" t="n"/>
-      <c r="D4" s="80" t="inlineStr">
+      <c r="C4" s="87" t="n"/>
+      <c r="D4" s="86" t="inlineStr">
         <is>
           <t>CATEGORÍA</t>
         </is>
       </c>
-      <c r="E4" s="81" t="n"/>
-      <c r="F4" s="80" t="inlineStr">
+      <c r="E4" s="87" t="n"/>
+      <c r="F4" s="86" t="inlineStr">
         <is>
           <t>MEJOR CRITERIO</t>
         </is>
       </c>
-      <c r="G4" s="81" t="n"/>
-      <c r="H4" s="80" t="inlineStr">
+      <c r="G4" s="87" t="n"/>
+      <c r="H4" s="86" t="inlineStr">
         <is>
           <t>A MEJORAR</t>
         </is>
       </c>
-      <c r="I4" s="81" t="n"/>
+      <c r="I4" s="87" t="n"/>
       <c r="J4" s="4" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="82">
+      <c r="B5" s="88">
         <f>IF(COUNT(FORMATO!C9:C16)=0,0,FORMATO!E17)</f>
         <v/>
       </c>
-      <c r="C5" s="83" t="n"/>
-      <c r="D5" s="84">
+      <c r="C5" s="89" t="n"/>
+      <c r="D5" s="90">
         <f>FORMATO!B18</f>
         <v/>
       </c>
-      <c r="E5" s="83" t="n"/>
-      <c r="F5" s="84">
+      <c r="E5" s="89" t="n"/>
+      <c r="F5" s="90">
         <f>IFERROR(INDEX(B26:B33,MATCH(MAX(C26:C33),C26:C33,0)),"")</f>
         <v/>
       </c>
-      <c r="G5" s="83" t="n"/>
-      <c r="H5" s="84">
+      <c r="G5" s="89" t="n"/>
+      <c r="H5" s="90">
         <f>IF(COUNT(C26:C33)=0,"",IFERROR(INDEX(B26:B33,MATCH(MIN(C26:C33),C26:C33,0)),""))</f>
         <v/>
       </c>
-      <c r="I5" s="83" t="n"/>
+      <c r="I5" s="89" t="n"/>
       <c r="J5" s="4" t="n"/>
     </row>
     <row r="6">
@@ -2660,12 +2871,12 @@
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>CRITERIO</t>
         </is>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>CALIFICACIÓN</t>
         </is>
@@ -2680,11 +2891,11 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
-      <c r="B26" s="52">
+      <c r="B26" s="57">
         <f>FORMATO!B9</f>
         <v/>
       </c>
-      <c r="C26" s="53">
+      <c r="C26" s="58">
         <f>IF(FORMATO!C9="",0,FORMATO!C9)</f>
         <v/>
       </c>
@@ -2698,11 +2909,11 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
-      <c r="B27" s="52">
+      <c r="B27" s="57">
         <f>FORMATO!B10</f>
         <v/>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="58">
         <f>IF(FORMATO!C10="",0,FORMATO!C10)</f>
         <v/>
       </c>
@@ -2716,11 +2927,11 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="52">
+      <c r="B28" s="57">
         <f>FORMATO!B11</f>
         <v/>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="58">
         <f>IF(FORMATO!C11="",0,FORMATO!C11)</f>
         <v/>
       </c>
@@ -2734,11 +2945,11 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="52">
+      <c r="B29" s="57">
         <f>FORMATO!B12</f>
         <v/>
       </c>
-      <c r="C29" s="53">
+      <c r="C29" s="58">
         <f>IF(FORMATO!C12="",0,FORMATO!C12)</f>
         <v/>
       </c>
@@ -2752,11 +2963,11 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="52">
+      <c r="B30" s="57">
         <f>FORMATO!B13</f>
         <v/>
       </c>
-      <c r="C30" s="53">
+      <c r="C30" s="58">
         <f>IF(FORMATO!C13="",0,FORMATO!C13)</f>
         <v/>
       </c>
@@ -2770,11 +2981,11 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
-      <c r="B31" s="52">
+      <c r="B31" s="57">
         <f>FORMATO!B14</f>
         <v/>
       </c>
-      <c r="C31" s="53">
+      <c r="C31" s="58">
         <f>IF(FORMATO!C14="",0,FORMATO!C14)</f>
         <v/>
       </c>
@@ -2788,11 +2999,11 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
-      <c r="B32" s="52">
+      <c r="B32" s="57">
         <f>FORMATO!B15</f>
         <v/>
       </c>
-      <c r="C32" s="53">
+      <c r="C32" s="58">
         <f>IF(FORMATO!C15="",0,FORMATO!C15)</f>
         <v/>
       </c>
@@ -2806,11 +3017,11 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
-      <c r="B33" s="52">
+      <c r="B33" s="57">
         <f>FORMATO!B16</f>
         <v/>
       </c>
-      <c r="C33" s="53">
+      <c r="C33" s="58">
         <f>IF(FORMATO!C16="",0,FORMATO!C16)</f>
         <v/>
       </c>
@@ -2871,7 +3082,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="54" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>AYUDA Y PREGUNTAS FRECUENTES</t>
         </is>
@@ -2880,7 +3091,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="55" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>EVALUACIÓN DE DESEMPEÑO</t>
         </is>
@@ -2915,12 +3126,12 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="56" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>¿Puedo cambiar los criterios?</t>
         </is>
       </c>
-      <c r="D6" s="57" t="inlineStr">
+      <c r="D6" s="62" t="inlineStr">
         <is>
           <t>Sí, edita el nombre y el peso; verifica que el total sea 100%.</t>
         </is>
@@ -2930,12 +3141,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="56" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>¿Qué hago con una calificación baja?</t>
         </is>
       </c>
-      <c r="D7" s="57" t="inlineStr">
+      <c r="D7" s="62" t="inlineStr">
         <is>
           <t>Acuerda un plan de acción con metas medibles y fecha de revisión.</t>
         </is>
@@ -2945,12 +3156,12 @@
     <row r="8" ht="53" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="56" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>¿Por qué no puedo escribir en algunas celdas?</t>
         </is>
       </c>
-      <c r="D8" s="57" t="inlineStr">
+      <c r="D8" s="62" t="inlineStr">
         <is>
           <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
         </is>
@@ -2960,12 +3171,12 @@
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="56" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>¿Cómo agrego mi logotipo?</t>
         </is>
       </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="D9" s="62" t="inlineStr">
         <is>
           <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
         </is>
@@ -2975,12 +3186,12 @@
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="56" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
         </is>
       </c>
-      <c r="D10" s="57" t="inlineStr">
+      <c r="D10" s="62" t="inlineStr">
         <is>
           <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
         </is>
@@ -2990,12 +3201,12 @@
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="56" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>¿Con qué versiones de Excel funciona?</t>
         </is>
       </c>
-      <c r="D11" s="57" t="inlineStr">
+      <c r="D11" s="62" t="inlineStr">
         <is>
           <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
         </is>
@@ -3005,14 +3216,14 @@
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
-      <c r="C12" s="56" t="inlineStr">
-        <is>
-          <t>¿Por qué la letra se ve diferente?</t>
-        </is>
-      </c>
-      <c r="D12" s="57" t="inlineStr">
-        <is>
-          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+      <c r="C12" s="61" t="inlineStr">
+        <is>
+          <t>¿Puedo cambiar la letra?</t>
+        </is>
+      </c>
+      <c r="D12" s="62" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Arial, disponible en Windows, Mac y Google Sheets. Si necesitas otra, selecciona todo (Ctrl+E) y cambia la fuente; no afecta el funcionamiento.</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -3020,12 +3231,12 @@
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="56" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>¿Puedo usarlo en varias empresas o por varios años?</t>
         </is>
       </c>
-      <c r="D13" s="57" t="inlineStr">
+      <c r="D13" s="62" t="inlineStr">
         <is>
           <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
         </is>
@@ -3053,12 +3264,12 @@
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="58" t="inlineStr">
+      <c r="C16" s="63" t="inlineStr">
         <is>
           <t>PONDERADO</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr">
+      <c r="D16" s="64" t="inlineStr">
         <is>
           <t>Calificación x peso del criterio.</t>
         </is>
@@ -3068,12 +3279,12 @@
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="58" t="inlineStr">
+      <c r="C17" s="63" t="inlineStr">
         <is>
           <t>SOBRESALIENTE</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr">
+      <c r="D17" s="64" t="inlineStr">
         <is>
           <t>Resultado &gt;= 4.5</t>
         </is>
@@ -3083,12 +3294,12 @@
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="58" t="inlineStr">
+      <c r="C18" s="63" t="inlineStr">
         <is>
           <t>SATISFACTORIO</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr">
+      <c r="D18" s="64" t="inlineStr">
         <is>
           <t>Resultado &gt;= 3.5</t>
         </is>
@@ -3098,12 +3309,12 @@
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="n"/>
-      <c r="C19" s="58" t="inlineStr">
+      <c r="C19" s="63" t="inlineStr">
         <is>
           <t>REQUIERE MEJORA</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr">
+      <c r="D19" s="64" t="inlineStr">
         <is>
           <t>Resultado &gt;= 2.5</t>
         </is>
@@ -3113,12 +3324,12 @@
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="4" t="n"/>
-      <c r="C20" s="58" t="inlineStr">
+      <c r="C20" s="63" t="inlineStr">
         <is>
           <t>DEFICIENTE</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr">
+      <c r="D20" s="64" t="inlineStr">
         <is>
           <t>Resultado &lt; 2.5</t>
         </is>
@@ -3145,12 +3356,12 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C23" s="61" t="inlineStr">
+      <c r="C23" s="66" t="inlineStr">
         <is>
           <t>Criterios acordados con el empleado</t>
         </is>
@@ -3159,12 +3370,12 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="B24" s="65" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C24" s="61" t="inlineStr">
+      <c r="C24" s="66" t="inlineStr">
         <is>
           <t>Evaluación llenada con evidencias</t>
         </is>
@@ -3173,12 +3384,12 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="B25" s="65" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C25" s="61" t="inlineStr">
+      <c r="C25" s="66" t="inlineStr">
         <is>
           <t>Retroalimentación realizada</t>
         </is>
@@ -3187,12 +3398,12 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="n"/>
-      <c r="B26" s="60" t="inlineStr">
+      <c r="B26" s="65" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C26" s="61" t="inlineStr">
+      <c r="C26" s="66" t="inlineStr">
         <is>
           <t>Plan de acción firmado</t>
         </is>
